--- a/TaskArrangement.xlsx
+++ b/TaskArrangement.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiverCG\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\TaskSemester\task_ShortSemester\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16630" windowHeight="12080" tabRatio="869"/>
+    <workbookView windowWidth="25600" windowHeight="12080" tabRatio="869"/>
   </bookViews>
   <sheets>
-    <sheet name="需求进度管理表" sheetId="71" r:id="rId1"/>
-    <sheet name="示例" sheetId="77" r:id="rId2"/>
+    <sheet name="需求进度管理表" sheetId="1" r:id="rId1"/>
+    <sheet name="示例" sheetId="2" r:id="rId2"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId3"/>
@@ -21,7 +21,6 @@
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="Activity">'[1]Data Definition'!#REF!</definedName>
@@ -34,8 +33,6 @@
     <definedName name="KOUMOKUSUU">#REF!</definedName>
     <definedName name="Module_num">#REF!</definedName>
     <definedName name="moduleList">OFFSET([2]Review记录!#REF!,0,0,COUNTA([2]Review记录!$K$1:$K$65536)-1,1)</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">示例!$1:$3</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">需求进度管理表!$1:$3</definedName>
     <definedName name="question">OFFSET([2]Review记录!$K$3,1,0,COUNTA([2]Review记录!$K$1:$K$65536)-1,1)</definedName>
     <definedName name="questionType">OFFSET([2]Review记录!$Q$3,1,0,COUNTA([2]Review记录!$K$1:$K$65536)-1,1)</definedName>
     <definedName name="reporter">OFFSET([2]Review记录!#REF!,0,0,COUNTA([2]Review记录!$K$1:$K$65536)-3,1)</definedName>
@@ -103,13 +100,15 @@
     <definedName name="信息内容">#REF!</definedName>
     <definedName name="需求开发工具">#REF!</definedName>
     <definedName name="需求信息">#REF!</definedName>
-    <definedName name="一级标题">[6]正文!$B$1</definedName>
+    <definedName name="一级标题">[5]正文!$B$1</definedName>
     <definedName name="约束条件">#REF!</definedName>
     <definedName name="运行环境">#REF!</definedName>
     <definedName name="质量保证计划">#REF!</definedName>
     <definedName name="子活动类型名">#REF!</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">需求进度管理表!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">示例!$1:$3</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -127,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="224">
   <si>
     <t>需求进度管理表</t>
   </si>
@@ -213,7 +212,7 @@
     <t>定位与地理编码</t>
   </si>
   <si>
-    <t>支持下拉选择区域或手动输入地址模拟GPS；调用百度/高德地图Web API将地址转换为经纬度。</t>
+    <t>支持下拉选择区域或手动输入地址模拟GPS；调用腾讯地图Web API将地址转换为经纬度。</t>
   </si>
   <si>
     <t>潘尹涛</t>
@@ -249,7 +248,10 @@
     <t>智能推荐电站</t>
   </si>
   <si>
-    <t>结合负荷（充电桩占用率）预测，在附近列表优先推荐低拥堵、高空闲率电站，并标注推荐标记。</t>
+    <t>结合负荷预测结果定推荐规则；潘尹涛在用户端列表（NO.5）加推荐标记，俞莫凡提供预测/规则数据。</t>
+  </si>
+  <si>
+    <t>俞莫凡</t>
   </si>
   <si>
     <t>一键导航</t>
@@ -258,7 +260,7 @@
     <t>地图加载与起终点</t>
   </si>
   <si>
-    <t>使用QWebEngineView加载百度/高德地图；起点为当前位置，终点为目标电站。</t>
+    <t>使用QWebEngineView加载腾讯地图；起点为当前位置，终点为目标电站。</t>
   </si>
   <si>
     <t>9.8</t>
@@ -270,7 +272,7 @@
     <t>出行方式与路线规划</t>
   </si>
   <si>
-    <t>提供驾车/步行选择；点击导航按钮跳转至百度/高德地图路线规划页面。</t>
+    <t>提供驾车/步行选择；点击导航按钮跳转至腾讯地图路线规划页面。</t>
   </si>
   <si>
     <t>用户信息维护</t>
@@ -342,10 +344,7 @@
     <t>Server API</t>
   </si>
   <si>
-    <t>用户端与管理端接口：找桩（list/detail 已完成）、充值/订单/收藏/统计/电桩/电站/用户/日志等；潘尹涛/韦迪安负责 UI 联调</t>
-  </si>
-  <si>
-    <t>陈戈/向泽涛</t>
+    <t>向泽涛独立实现全部业务 API（充值/订单/收藏/统计/电桩/电站/用户/日志等）；潘尹涛/韦迪安只做 UI 联调，不写 server。</t>
   </si>
   <si>
     <t>PC服务器端</t>
@@ -357,7 +356,7 @@
     <t>账号密码登录</t>
   </si>
   <si>
-    <t>输入账号/密码对照管理员表校验；默认初始账号 admin/123456；成功进入宽屏管理主界面。</t>
+    <t>输入账号/密码对照管理员表校验；默认初始账号admin/123456；成功进入宽屏管理主界面。</t>
   </si>
   <si>
     <t>韦迪安</t>
@@ -390,7 +389,7 @@
     <t>状态分布与健康度</t>
   </si>
   <si>
-    <t>表格展示在用、闲置、故障的数量及占比百分比，直观反映设备整体运行健康度。</t>
+    <t>韦迪安用QChart展示状态分布；统计数据口径与俞莫凡NO.35分析表对齐。</t>
   </si>
   <si>
     <t>需使用QChart</t>
@@ -399,7 +398,7 @@
     <t>负荷预警看板</t>
   </si>
   <si>
-    <t>接收预测结果，对高峰、低空闲率站点预警，辅助值守与电力调配。</t>
+    <t>俞莫凡定义预警规则并供数；韦迪安在管理端看板（NO.48）展示预警列表。</t>
   </si>
   <si>
     <t>充电桩管理</t>
@@ -420,7 +419,7 @@
     <t>电桩更新</t>
   </si>
   <si>
-    <t>新增电站中的电桩，删除指定电桩，修改电桩信息、状态</t>
+    <t>新增电站中的电桩，删除指定电桩，修改电桩信息、状态。</t>
   </si>
   <si>
     <t>充电站管理</t>
@@ -489,7 +488,7 @@
     <t>预测表、日志与约束</t>
   </si>
   <si>
-    <t>保存负荷预测与操作日志；主键外键、手机号唯一、余额非负；密码不明文；支持库文件备份。</t>
+    <t>俞莫凡设计预测表/分析表结构与 seed；陈戈协助操作日志表与安全约束（外键/非负/备份）。</t>
   </si>
   <si>
     <t>大数据可视化大屏</t>
@@ -498,37 +497,58 @@
     <t>采集与治理</t>
   </si>
   <si>
-    <t>数据采集与存储</t>
-  </si>
-  <si>
-    <t>定时从业务库采集订单、电桩状态、用户与营收数据，聚合结果落分析表，避免大屏直查压库。</t>
-  </si>
-  <si>
-    <t>俞莫凡</t>
-  </si>
-  <si>
-    <t>预处理与指标分析</t>
-  </si>
-  <si>
-    <t>去重、补全、过滤异常订单；按日/站/桩聚合，计算利用率、故障率、高峰时段、区域分布等指标。</t>
+    <t>数据采集脚本与定时调度</t>
+  </si>
+  <si>
+    <t>Python 脚本定时从charge.db采集订单、电桩状态、用户与营收数据；写入分析表，避免大屏直查压库。</t>
+  </si>
+  <si>
+    <t>分析表聚合与读接口</t>
+  </si>
+  <si>
+    <t>向泽涛在server提供stats/forecast只读接口；聚合SQL口径与俞莫凡NO.35对齐。</t>
+  </si>
+  <si>
+    <t>数据清洗与异常过滤</t>
+  </si>
+  <si>
+    <t>去重、补全、过滤异常订单与脏数据；输出清洗日志，规则由陈戈与俞莫凡共同评审。</t>
+  </si>
+  <si>
+    <t>运营指标计算</t>
+  </si>
+  <si>
+    <t>按日/站/桩聚合利用率、故障率、高峰时段；韦迪安在大屏 NO.41 与管理端复用同一套指标。</t>
   </si>
   <si>
     <t>展示与部署</t>
   </si>
   <si>
-    <t>ECharts运营看板</t>
-  </si>
-  <si>
-    <t>Web大屏用ECharts展示营收趋势、电桩状态占比、站点负荷、用户规模等，面向运营决策。</t>
-  </si>
-  <si>
-    <t>预测结果上屏</t>
-  </si>
-  <si>
-    <t>接入负荷预测，展示未来1小时、6小时、24小时各站点负荷与空闲桩数量。</t>
-  </si>
-  <si>
-    <t>需使用ECharts</t>
+    <t>Flask 大屏后端框架</t>
+  </si>
+  <si>
+    <t>搭建Flask项目结构、路由、模板；连接charge.db/analysis表，提供REST页面数据。</t>
+  </si>
+  <si>
+    <t>ECharts 营收与桩状态图表</t>
+  </si>
+  <si>
+    <t>大屏展示营收趋势折线、电桩状态占比饼图；支持日/周切换刷新。</t>
+  </si>
+  <si>
+    <t>需使用 ECharts</t>
+  </si>
+  <si>
+    <t>ECharts 区域负荷与站点分布</t>
+  </si>
+  <si>
+    <t>地图或柱状图展示各区域负荷、站点分布与用户规模，面向运营决策。</t>
+  </si>
+  <si>
+    <t>预测结果大屏展示</t>
+  </si>
+  <si>
+    <t>接入俞莫凡NO.45预测结果，展示未来1/6/24小时各站点负荷与空闲桩数量。</t>
   </si>
   <si>
     <t>机器学习智能分析</t>
@@ -537,31 +557,55 @@
     <t>充电负荷智能预测</t>
   </si>
   <si>
-    <t>特征工程与模型训练</t>
-  </si>
-  <si>
-    <t>提取充电时段、时长、电量、出行时段及天气、节假日等特征，用时序算法（或基线平滑）建模。</t>
+    <t>特征工程与训练数据集</t>
+  </si>
+  <si>
+    <t>提取充电时段、时长、电量、出行时段及天气、节假日等特征，构建训练/验证集。</t>
+  </si>
+  <si>
+    <t>时序模型训练与评估</t>
+  </si>
+  <si>
+    <t>用时序算法（ARIMA/移动平均/轻量 LSTM等）训练模型，输出 MAE/RMSE 评估报告。</t>
   </si>
   <si>
     <t>同需要预测功能</t>
   </si>
   <si>
-    <t>多步负荷预测</t>
-  </si>
-  <si>
-    <t>预测未来1/6/24小时各站充电负荷、空闲桩数、高峰时段，结果写入预测表。</t>
-  </si>
-  <si>
-    <t>智能推荐与运营预警</t>
-  </si>
-  <si>
-    <t>用户端优先推荐低拥堵高空闲率电站；运营端提供负荷预警，辅助电力调配与值守。</t>
-  </si>
-  <si>
-    <t>故障诊断与智能风控</t>
-  </si>
-  <si>
-    <t>识别异常桩（长占用无订单、频繁离线等）；检测异常充电行为，提供冻结账户建议。</t>
+    <t>多步负荷预测写入</t>
+  </si>
+  <si>
+    <t>预测未来1/6/24小时各站充电负荷、空闲桩数，结果写入forecast表；向泽涛提供读取 API。</t>
+  </si>
+  <si>
+    <t>forecast API 与智能推荐对接</t>
+  </si>
+  <si>
+    <t>向泽涛实现forecast.list；潘尹涛在用户端对接NO.7智能推荐展示。</t>
+  </si>
+  <si>
+    <t>用户端推荐展示与联调</t>
+  </si>
+  <si>
+    <t>潘尹涛在用户端列表/详情接入推荐标记与 forecast 数据，与 NO.7、NO.47 API 联调。</t>
+  </si>
+  <si>
+    <t>运营负荷预警与管理端对接</t>
+  </si>
+  <si>
+    <t>韦迪安将预测高峰/低谷空闲率站点推送到管理端负荷预警看板（对接 NO.24）。</t>
+  </si>
+  <si>
+    <t>异常电桩检测与告警</t>
+  </si>
+  <si>
+    <t>识别长占用无订单、频繁离线等异常桩，生成告警记录写入日志表。</t>
+  </si>
+  <si>
+    <t>异常充电行为与风控建议</t>
+  </si>
+  <si>
+    <t>陈戈定义风控规则；向泽涛实现检测逻辑，管理端展示冻结建议列表。</t>
   </si>
   <si>
     <t>出错与安全</t>
@@ -762,19 +806,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="7">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="&quot;\&quot;#,##0.00;[Red]&quot;\&quot;\-#,##0.00"/>
     <numFmt numFmtId="177" formatCode="&quot;\&quot;#,##0;[Red]&quot;\&quot;\-#,##0"/>
     <numFmt numFmtId="178" formatCode="mmm"/>
     <numFmt numFmtId="179" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="181" formatCode="_(&quot;\&quot;* #,##0_);_(&quot;\&quot;* \(#,##0\);_(&quot;\&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="182" formatCode="_(&quot;\&quot;* #,##0_);_(&quot;\&quot;* \(#,##0\);_(&quot;\&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="_(&quot;\&quot;* #,##0_);_(&quot;\&quot;* \(#,##0\);_(&quot;\&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="181" formatCode="_(&quot;\&quot;* #,##0_);_(&quot;\&quot;* \(#,##0\);_(&quot;\&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="36">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="2"/>
       <charset val="254"/>
     </font>
     <font>
@@ -934,32 +977,27 @@
       <b/>
       <sz val="10"/>
       <name val="MS Sans Serif"/>
-      <family val="2"/>
       <charset val="0"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="MS Sans Serif"/>
-      <family val="2"/>
       <charset val="0"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="254"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="254"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <charset val="254"/>
     </font>
     <font>
@@ -967,7 +1005,6 @@
       <sz val="11"/>
       <color indexed="36"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="2"/>
       <charset val="254"/>
     </font>
     <font>
@@ -975,13 +1012,11 @@
       <sz val="10"/>
       <color indexed="12"/>
       <name val="Arial"/>
-      <family val="2"/>
       <charset val="254"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="黑体"/>
-      <family val="3"/>
       <charset val="254"/>
     </font>
     <font>
@@ -998,7 +1033,6 @@
     <font>
       <sz val="10"/>
       <name val="Helv"/>
-      <family val="2"/>
       <charset val="0"/>
     </font>
   </fonts>
@@ -1142,7 +1176,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -1318,19 +1352,6 @@
         <color auto="1"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
         <color indexed="8"/>
       </right>
       <top style="thin">
@@ -1362,49 +1383,6 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1540,162 +1518,162 @@
   </borders>
   <cellStyleXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="40" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="40" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="19">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="20">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="19">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="21">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="23">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="15" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="29">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="25">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -1703,19 +1681,17 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="60" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="60" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="60" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1744,7 +1720,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="59" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="59" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1793,50 +1769,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="60" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="3" xfId="60" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="17" xfId="60" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="60" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="72">
@@ -1981,11 +1926,6 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
-    <mruColors>
-      <color rgb="00FF0000"/>
-      <color rgb="0099CCFF"/>
-      <color rgb="00000000"/>
-    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2148,41 +2088,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="文件封面"/>
-      <sheetName val="文件修改控制"/>
-      <sheetName val="封面"/>
-      <sheetName val="变更履历"/>
-      <sheetName val="目录"/>
-      <sheetName val="配置管理计划"/>
-      <sheetName val="配置库结构&amp;权限"/>
-      <sheetName val="资料管理"/>
-      <sheetName val="基准状态记录"/>
-      <sheetName val="变更请求记录"/>
-      <sheetName val="配置审计记录"/>
-      <sheetName val="需求与成果物对应关系表"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2488,1581 +2393,1742 @@
   <dimension ref="B1:J168"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="1.63636363636364" style="3" customWidth="1"/>
-    <col min="2" max="2" width="4.45454545454545" style="4"/>
-    <col min="3" max="4" width="16.6363636363636" style="4" customWidth="1"/>
-    <col min="5" max="5" width="22" style="4" customWidth="1"/>
-    <col min="6" max="6" width="57.1818181818182" style="4" customWidth="1"/>
-    <col min="7" max="7" width="9.84545454545455" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10.4545454545455" style="5"/>
-    <col min="9" max="9" width="6.36363636363636" style="5"/>
-    <col min="10" max="10" width="22.0909090909091" style="6"/>
-    <col min="11" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="1.63636363636364" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.45454545454545" style="2" customWidth="1"/>
+    <col min="3" max="4" width="16.6363636363636" style="2" customWidth="1"/>
+    <col min="5" max="5" width="22" style="2" customWidth="1"/>
+    <col min="6" max="6" width="57.1818181818182" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.84545454545455" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.4545454545455" style="3" customWidth="1"/>
+    <col min="9" max="9" width="6.36363636363636" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.0909090909091" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="41.25" customHeight="1" spans="2:10">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" ht="21" customHeight="1" spans="2:10">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:10">
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B4" s="29">
+    <row r="4" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B4" s="27">
         <v>1</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="33"/>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="2:10">
-      <c r="B5" s="29">
+      <c r="J4" s="30"/>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B5" s="27">
         <v>2</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="31" t="s">
+      <c r="C5" s="31"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="33"/>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B6" s="29">
+      <c r="J5" s="30"/>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B6" s="27">
         <v>3</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="31" t="s">
+      <c r="C6" s="32"/>
+      <c r="D6" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="H6" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="33"/>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B7" s="29">
+      <c r="J6" s="30"/>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B7" s="27">
         <v>4</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="32" t="s">
+      <c r="H7" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J7" s="36" t="s">
+      <c r="J7" s="33" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B8" s="29">
+    <row r="8" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B8" s="27">
         <v>5</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="31" t="s">
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="G8" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I8" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="36" t="s">
+      <c r="J8" s="33" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B9" s="29">
+    <row r="9" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B9" s="27">
         <v>6</v>
       </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="31" t="s">
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I9" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J9" s="33"/>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B10" s="29">
+      <c r="J9" s="30"/>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B10" s="27">
         <v>7</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="31" t="s">
+      <c r="C10" s="31"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="30"/>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B11" s="27">
+        <v>8</v>
+      </c>
+      <c r="C11" s="31"/>
+      <c r="D11" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G11" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="H11" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J11" s="33" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B12" s="27">
+        <v>9</v>
+      </c>
+      <c r="C12" s="31"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="30"/>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B13" s="27">
+        <v>10</v>
+      </c>
+      <c r="C13" s="31"/>
+      <c r="D13" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="30"/>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B14" s="27">
+        <v>11</v>
+      </c>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B15" s="27">
+        <v>12</v>
+      </c>
+      <c r="C15" s="31"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="30"/>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B16" s="27">
+        <v>13</v>
+      </c>
+      <c r="C16" s="31"/>
+      <c r="D16" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="30"/>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B17" s="27">
+        <v>14</v>
+      </c>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="30"/>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B18" s="27">
+        <v>15</v>
+      </c>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="30"/>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B19" s="27">
+        <v>16</v>
+      </c>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H19" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J19" s="30"/>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B20" s="27">
+        <v>17</v>
+      </c>
+      <c r="C20" s="31"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I20" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="33"/>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B11" s="29">
-        <v>8</v>
-      </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="30" t="s">
+      <c r="J20" s="30"/>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B21" s="27">
+        <v>18</v>
+      </c>
+      <c r="C21" s="32"/>
+      <c r="D21" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" s="30"/>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B22" s="27">
+        <v>19</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H22" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="30"/>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B23" s="27">
+        <v>20</v>
+      </c>
+      <c r="C23" s="31"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J23" s="30"/>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B24" s="27">
+        <v>21</v>
+      </c>
+      <c r="C24" s="31"/>
+      <c r="D24" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H24" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" s="30"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B25" s="27">
+        <v>22</v>
+      </c>
+      <c r="C25" s="31"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="30"/>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B26" s="27">
+        <v>23</v>
+      </c>
+      <c r="C26" s="31"/>
+      <c r="D26" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="33" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B27" s="27">
+        <v>24</v>
+      </c>
+      <c r="C27" s="31"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="28" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="G27" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="H27" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J27" s="30"/>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="24" customHeight="1" spans="2:10">
+      <c r="B28" s="27">
+        <v>25</v>
+      </c>
+      <c r="C28" s="31"/>
+      <c r="D28" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" s="30"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:10">
+      <c r="B29" s="27">
+        <v>26</v>
+      </c>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" s="30"/>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="2:10">
+      <c r="B30" s="27">
+        <v>27</v>
+      </c>
+      <c r="C30" s="31"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H30" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" s="30"/>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="2:10">
+      <c r="B31" s="27">
+        <v>28</v>
+      </c>
+      <c r="C31" s="31"/>
+      <c r="D31" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="F31" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H31" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J31" s="30"/>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="2:10">
+      <c r="B32" s="27">
+        <v>29</v>
+      </c>
+      <c r="C32" s="31"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="F32" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H32" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J32" s="30"/>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="2:10">
+      <c r="B33" s="27">
+        <v>30</v>
+      </c>
+      <c r="C33" s="31"/>
+      <c r="D33" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="E33" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H33" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="30"/>
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="2:10">
+      <c r="B34" s="27">
+        <v>31</v>
+      </c>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H34" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" s="30"/>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="2:10">
+      <c r="B35" s="27">
+        <v>32</v>
+      </c>
+      <c r="C35" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="J35" s="30"/>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="2:10">
+      <c r="B36" s="27">
+        <v>33</v>
+      </c>
+      <c r="C36" s="31"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="F36" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="J36" s="30"/>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="2:10">
+      <c r="B37" s="27">
+        <v>34</v>
+      </c>
+      <c r="C37" s="31"/>
+      <c r="D37" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="E37" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="F37" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="J37" s="30"/>
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="2:10">
+      <c r="B38" s="27">
+        <v>35</v>
+      </c>
+      <c r="C38" s="32"/>
+      <c r="D38" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="F38" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H38" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="J38" s="30"/>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="2:10">
+      <c r="B39" s="27">
+        <v>36</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="D39" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E39" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="F39" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H39" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J39" s="30"/>
+    </row>
+    <row r="40" ht="24" customHeight="1" spans="2:10">
+      <c r="B40" s="27">
+        <v>37</v>
+      </c>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F40" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H40" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" s="30"/>
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="2:10">
+      <c r="B41" s="27">
+        <v>38</v>
+      </c>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="F41" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="I41" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J41" s="30"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="2:10">
+      <c r="B42" s="27">
+        <v>39</v>
+      </c>
+      <c r="C42" s="31"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="F42" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H42" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="I42" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J42" s="30"/>
+    </row>
+    <row r="43" ht="24" customHeight="1" spans="2:10">
+      <c r="B43" s="27">
+        <v>40</v>
+      </c>
+      <c r="C43" s="31"/>
+      <c r="D43" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="F43" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H43" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="I43" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J43" s="30"/>
+    </row>
+    <row r="44" ht="24" customHeight="1" spans="2:10">
+      <c r="B44" s="27">
+        <v>41</v>
+      </c>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F44" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H44" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I44" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J44" s="33" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1" spans="2:10">
+      <c r="B45" s="27">
         <v>42</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="F45" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H45" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I45" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J45" s="30"/>
+    </row>
+    <row r="46" ht="24" customHeight="1" spans="2:10">
+      <c r="B46" s="27">
         <v>43</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="F46" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H46" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J46" s="30"/>
+    </row>
+    <row r="47" ht="24" customHeight="1" spans="2:10">
+      <c r="B47" s="27">
+        <v>44</v>
+      </c>
+      <c r="C47" s="28" t="s">
+        <v>141</v>
+      </c>
+      <c r="D47" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="F47" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H47" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="I47" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J47" s="30"/>
+    </row>
+    <row r="48" ht="24" customHeight="1" spans="2:10">
+      <c r="B48" s="27">
+        <v>45</v>
+      </c>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="28" t="s">
+        <v>145</v>
+      </c>
+      <c r="F48" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H48" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I48" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J48" s="33" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1" spans="2:10">
+      <c r="B49" s="27">
+        <v>46</v>
+      </c>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="F49" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H49" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="I49" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J49" s="30"/>
+    </row>
+    <row r="50" ht="24" customHeight="1" spans="2:10">
+      <c r="B50" s="27">
+        <v>47</v>
+      </c>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="F50" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H50" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J50" s="30"/>
+    </row>
+    <row r="51" ht="24" customHeight="1" spans="2:10">
+      <c r="B51" s="27">
+        <v>48</v>
+      </c>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="F51" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H51" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J51" s="30"/>
+    </row>
+    <row r="52" ht="24" customHeight="1" spans="2:10">
+      <c r="B52" s="27">
+        <v>49</v>
+      </c>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="F52" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H52" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J52" s="30"/>
+    </row>
+    <row r="53" ht="24" customHeight="1" spans="2:10">
+      <c r="B53" s="27">
+        <v>50</v>
+      </c>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="F53" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="H53" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="J53" s="30"/>
+    </row>
+    <row r="54" ht="24" customHeight="1" spans="2:10">
+      <c r="B54" s="27">
+        <v>51</v>
+      </c>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="F54" s="28" t="s">
+        <v>159</v>
+      </c>
+      <c r="G54" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" s="18" t="s">
+      <c r="H54" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I54" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J11" s="36" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" spans="2:10">
-      <c r="B12" s="29">
-        <v>9</v>
-      </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="18" t="s">
+      <c r="J54" s="30"/>
+    </row>
+    <row r="55" ht="24" customHeight="1" spans="2:10">
+      <c r="B55" s="27">
+        <v>52</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="D55" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="E55" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="F55" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="G55" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="18" t="s">
+      <c r="H55" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I55" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="30"/>
+    </row>
+    <row r="56" ht="24" customHeight="1" spans="2:10">
+      <c r="B56" s="27">
+        <v>53</v>
+      </c>
+      <c r="C56" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="E56" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="F56" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I56" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="33"/>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B13" s="29">
-        <v>10</v>
-      </c>
-      <c r="C13" s="34"/>
-      <c r="D13" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="33"/>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="36" spans="2:10">
-      <c r="B14" s="29">
-        <v>11</v>
-      </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="I14" s="18" t="s">
+      <c r="J56" s="30"/>
+    </row>
+    <row r="57" ht="24" customHeight="1" spans="2:10">
+      <c r="B57" s="27">
+        <v>54</v>
+      </c>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="F57" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="I57" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J14" s="36" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="2:10">
-      <c r="B15" s="29">
-        <v>12</v>
-      </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J15" s="33"/>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B16" s="29">
-        <v>13</v>
-      </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H16" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J16" s="33"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="2:10">
-      <c r="B17" s="29">
-        <v>14</v>
-      </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H17" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J17" s="33"/>
-    </row>
-    <row r="18" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B18" s="29">
-        <v>15</v>
-      </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H18" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J18" s="33"/>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="2:10">
-      <c r="B19" s="29">
-        <v>16</v>
-      </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H19" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" s="33"/>
-    </row>
-    <row r="20" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B20" s="29">
-        <v>17</v>
-      </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="H20" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J20" s="33"/>
-    </row>
-    <row r="21" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B21" s="29">
-        <v>18</v>
-      </c>
-      <c r="C21" s="34"/>
-      <c r="D21" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="E21" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="H21" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" s="33"/>
-    </row>
-    <row r="22" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B22" s="29">
-        <v>19</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="G22" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H22" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="I22" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="33"/>
-    </row>
-    <row r="23" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B23" s="29">
-        <v>20</v>
-      </c>
-      <c r="C23" s="34"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H23" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" s="33"/>
-    </row>
-    <row r="24" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B24" s="29">
-        <v>21</v>
-      </c>
-      <c r="C24" s="34"/>
-      <c r="D24" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="F24" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H24" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="I24" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J24" s="33"/>
-    </row>
-    <row r="25" s="2" customFormat="1" spans="2:10">
-      <c r="B25" s="29">
-        <v>22</v>
-      </c>
-      <c r="C25" s="34"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="F25" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="G25" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H25" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="I25" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25" s="33"/>
-    </row>
-    <row r="26" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B26" s="29">
-        <v>23</v>
-      </c>
-      <c r="C26" s="34"/>
-      <c r="D26" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="F26" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H26" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="I26" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J26" s="36" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" spans="2:10">
-      <c r="B27" s="29">
-        <v>24</v>
-      </c>
-      <c r="C27" s="34"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="31" t="s">
-        <v>89</v>
-      </c>
-      <c r="F27" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H27" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J27" s="33"/>
-    </row>
-    <row r="28" s="2" customFormat="1" ht="24" spans="2:10">
-      <c r="B28" s="29">
-        <v>25</v>
-      </c>
-      <c r="C28" s="34"/>
-      <c r="D28" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="E28" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="F28" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="G28" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H28" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="I28" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J28" s="33"/>
-    </row>
-    <row r="29" spans="2:10">
-      <c r="B29" s="29">
-        <v>26</v>
-      </c>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="G29" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H29" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="I29" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J29" s="33"/>
-    </row>
-    <row r="30" spans="2:10">
-      <c r="B30" s="29">
-        <v>27</v>
-      </c>
-      <c r="C30" s="34"/>
-      <c r="D30" s="35"/>
-      <c r="E30" s="18" t="s">
-        <v>96</v>
-      </c>
-      <c r="F30" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="G30" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H30" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="I30" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J30" s="33"/>
-    </row>
-    <row r="31" ht="24" spans="2:10">
-      <c r="B31" s="29">
-        <v>28</v>
-      </c>
-      <c r="C31" s="34"/>
-      <c r="D31" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="F31" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="G31" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H31" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="I31" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J31" s="33"/>
-    </row>
-    <row r="32" ht="24" spans="2:10">
-      <c r="B32" s="29">
-        <v>29</v>
-      </c>
-      <c r="C32" s="34"/>
-      <c r="D32" s="38"/>
-      <c r="E32" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="F32" s="31" t="s">
-        <v>102</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H32" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="I32" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J32" s="33"/>
-    </row>
-    <row r="33" ht="24" spans="2:10">
-      <c r="B33" s="29">
-        <v>30</v>
-      </c>
-      <c r="C33" s="34"/>
-      <c r="D33" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="F33" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="G33" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H33" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="I33" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J33" s="33"/>
-    </row>
-    <row r="34" spans="2:10">
-      <c r="B34" s="29">
-        <v>31</v>
-      </c>
-      <c r="C34" s="35"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="F34" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="G34" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H34" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="I34" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J34" s="33"/>
-    </row>
-    <row r="35" ht="24" spans="2:10">
-      <c r="B35" s="29">
-        <v>32</v>
-      </c>
-      <c r="C35" s="37" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="F35" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="G35" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="J35" s="33"/>
-    </row>
-    <row r="36" ht="24" spans="2:10">
-      <c r="B36" s="29">
-        <v>33</v>
-      </c>
-      <c r="C36" s="39"/>
-      <c r="D36" s="38"/>
-      <c r="E36" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="F36" s="31" t="s">
-        <v>114</v>
-      </c>
-      <c r="G36" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="I36" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="J36" s="33"/>
-    </row>
-    <row r="37" spans="2:10">
-      <c r="B37" s="29">
-        <v>34</v>
-      </c>
-      <c r="C37" s="39"/>
-      <c r="D37" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="E37" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="F37" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="G37" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H37" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="I37" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="J37" s="33"/>
-    </row>
-    <row r="38" ht="24" spans="2:10">
-      <c r="B38" s="29">
-        <v>35</v>
-      </c>
-      <c r="C38" s="38"/>
-      <c r="D38" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>119</v>
-      </c>
-      <c r="F38" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="G38" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H38" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="I38" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="J38" s="33"/>
-    </row>
-    <row r="39" ht="24" spans="2:10">
-      <c r="B39" s="29">
-        <v>36</v>
-      </c>
-      <c r="C39" s="37" t="s">
-        <v>121</v>
-      </c>
-      <c r="D39" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="E39" s="18" t="s">
-        <v>123</v>
-      </c>
-      <c r="F39" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="G39" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H39" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="I39" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J39" s="33"/>
-    </row>
-    <row r="40" ht="24" spans="2:10">
-      <c r="B40" s="29">
-        <v>37</v>
-      </c>
-      <c r="C40" s="39"/>
-      <c r="D40" s="38"/>
-      <c r="E40" s="18" t="s">
-        <v>126</v>
-      </c>
-      <c r="F40" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="G40" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H40" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="I40" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J40" s="33"/>
-    </row>
-    <row r="41" ht="24" spans="2:10">
-      <c r="B41" s="29">
-        <v>38</v>
-      </c>
-      <c r="C41" s="39"/>
-      <c r="D41" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="F41" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="G41" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H41" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="I41" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J41" s="33"/>
-    </row>
-    <row r="42" spans="2:10">
-      <c r="B42" s="29">
-        <v>39</v>
-      </c>
-      <c r="C42" s="38"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="F42" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H42" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="I42" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J42" s="36" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="43" ht="24" spans="2:10">
-      <c r="B43" s="29">
-        <v>40</v>
-      </c>
-      <c r="C43" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="D43" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="E43" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="F43" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="G43" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H43" s="32" t="s">
-        <v>61</v>
-      </c>
-      <c r="I43" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J43" s="36" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10">
-      <c r="B44" s="29">
-        <v>41</v>
-      </c>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="F44" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="G44" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H44" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="I44" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J44" s="33"/>
-    </row>
-    <row r="45" ht="24" spans="2:10">
-      <c r="B45" s="29">
-        <v>42</v>
-      </c>
-      <c r="C45" s="39"/>
-      <c r="D45" s="39"/>
-      <c r="E45" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="F45" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="G45" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H45" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="I45" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J45" s="33"/>
-    </row>
-    <row r="46" ht="24" spans="2:10">
-      <c r="B46" s="29">
-        <v>43</v>
-      </c>
-      <c r="C46" s="38"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="F46" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="G46" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="H46" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="I46" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J46" s="33"/>
-    </row>
-    <row r="47" ht="36" spans="2:10">
-      <c r="B47" s="29">
-        <v>44</v>
-      </c>
-      <c r="C47" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="D47" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E47" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="F47" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="G47" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="H47" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="I47" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="33"/>
-    </row>
-    <row r="48" ht="36" spans="2:10">
-      <c r="B48" s="29">
-        <v>45</v>
-      </c>
-      <c r="C48" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="E48" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="F48" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="G48" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H48" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="I48" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="J48" s="33"/>
-    </row>
-    <row r="49" ht="36" spans="2:10">
-      <c r="B49" s="29">
-        <v>46</v>
-      </c>
-      <c r="C49" s="40"/>
-      <c r="D49" s="40"/>
-      <c r="E49" s="41" t="s">
-        <v>151</v>
-      </c>
-      <c r="F49" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="G49" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H49" s="43" t="s">
-        <v>24</v>
-      </c>
-      <c r="I49" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="J49" s="44"/>
-    </row>
-    <row r="50" spans="2:10">
-      <c r="B50" s="25"/>
-    </row>
-    <row r="51" spans="2:10">
-      <c r="B51" s="25"/>
-    </row>
-    <row r="52" spans="2:10">
-      <c r="B52" s="25"/>
-    </row>
-    <row r="53" spans="2:10">
-      <c r="B53" s="25"/>
-    </row>
-    <row r="54" spans="2:10">
-      <c r="B54" s="25"/>
-    </row>
-    <row r="55" spans="2:10">
-      <c r="B55" s="25"/>
-    </row>
-    <row r="56" spans="2:10">
-      <c r="B56" s="25"/>
-    </row>
-    <row r="57" spans="2:10">
-      <c r="B57" s="25"/>
+      <c r="J57" s="30"/>
     </row>
     <row r="58" spans="2:10">
-      <c r="B58" s="25"/>
+      <c r="B58" s="23"/>
     </row>
     <row r="59" spans="2:10">
-      <c r="B59" s="25"/>
+      <c r="B59" s="23"/>
     </row>
     <row r="60" spans="2:10">
-      <c r="B60" s="25"/>
+      <c r="B60" s="23"/>
     </row>
     <row r="61" spans="2:10">
-      <c r="B61" s="25"/>
+      <c r="B61" s="23"/>
     </row>
     <row r="62" spans="2:10">
-      <c r="B62" s="25"/>
+      <c r="B62" s="23"/>
     </row>
     <row r="63" spans="2:10">
-      <c r="B63" s="25"/>
+      <c r="B63" s="23"/>
     </row>
     <row r="64" spans="2:10">
-      <c r="B64" s="25"/>
+      <c r="B64" s="23"/>
     </row>
     <row r="65" spans="2:2">
-      <c r="B65" s="25"/>
+      <c r="B65" s="23"/>
     </row>
     <row r="66" spans="2:2">
-      <c r="B66" s="25"/>
+      <c r="B66" s="23"/>
     </row>
     <row r="67" spans="2:2">
-      <c r="B67" s="25"/>
+      <c r="B67" s="23"/>
     </row>
     <row r="68" spans="2:2">
-      <c r="B68" s="25"/>
+      <c r="B68" s="23"/>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" s="25"/>
+      <c r="B69" s="23"/>
     </row>
     <row r="70" spans="2:2">
-      <c r="B70" s="25"/>
+      <c r="B70" s="23"/>
     </row>
     <row r="71" spans="2:2">
-      <c r="B71" s="25"/>
+      <c r="B71" s="23"/>
     </row>
     <row r="72" spans="2:2">
-      <c r="B72" s="25"/>
+      <c r="B72" s="23"/>
     </row>
     <row r="73" spans="2:2">
-      <c r="B73" s="25"/>
+      <c r="B73" s="23"/>
     </row>
     <row r="74" spans="2:2">
-      <c r="B74" s="25"/>
+      <c r="B74" s="23"/>
     </row>
     <row r="75" spans="2:2">
-      <c r="B75" s="25"/>
+      <c r="B75" s="23"/>
     </row>
     <row r="76" spans="2:2">
-      <c r="B76" s="25"/>
+      <c r="B76" s="23"/>
     </row>
     <row r="77" spans="2:2">
-      <c r="B77" s="25"/>
+      <c r="B77" s="23"/>
     </row>
     <row r="78" spans="2:2">
-      <c r="B78" s="25"/>
+      <c r="B78" s="23"/>
     </row>
     <row r="79" spans="2:2">
-      <c r="B79" s="25"/>
+      <c r="B79" s="23"/>
     </row>
     <row r="80" spans="2:2">
-      <c r="B80" s="25"/>
+      <c r="B80" s="23"/>
     </row>
     <row r="81" spans="2:2">
-      <c r="B81" s="25"/>
+      <c r="B81" s="23"/>
     </row>
     <row r="82" spans="2:2">
-      <c r="B82" s="25"/>
+      <c r="B82" s="23"/>
     </row>
     <row r="83" spans="2:2">
-      <c r="B83" s="25"/>
+      <c r="B83" s="23"/>
     </row>
     <row r="84" spans="2:2">
-      <c r="B84" s="25"/>
+      <c r="B84" s="23"/>
     </row>
     <row r="85" spans="2:2">
-      <c r="B85" s="25"/>
+      <c r="B85" s="23"/>
     </row>
     <row r="86" spans="2:2">
-      <c r="B86" s="25"/>
+      <c r="B86" s="23"/>
     </row>
     <row r="87" spans="2:2">
-      <c r="B87" s="25"/>
+      <c r="B87" s="23"/>
     </row>
     <row r="88" spans="2:2">
-      <c r="B88" s="25"/>
+      <c r="B88" s="23"/>
     </row>
     <row r="89" spans="2:2">
-      <c r="B89" s="25"/>
+      <c r="B89" s="23"/>
     </row>
     <row r="90" spans="2:2">
-      <c r="B90" s="25"/>
+      <c r="B90" s="23"/>
     </row>
     <row r="91" spans="2:2">
-      <c r="B91" s="25"/>
+      <c r="B91" s="23"/>
     </row>
     <row r="92" spans="2:2">
-      <c r="B92" s="25"/>
+      <c r="B92" s="23"/>
     </row>
     <row r="93" spans="2:2">
-      <c r="B93" s="25"/>
+      <c r="B93" s="23"/>
     </row>
     <row r="94" spans="2:2">
-      <c r="B94" s="25"/>
+      <c r="B94" s="23"/>
     </row>
     <row r="95" spans="2:2">
-      <c r="B95" s="25"/>
+      <c r="B95" s="23"/>
     </row>
     <row r="96" spans="2:2">
-      <c r="B96" s="25"/>
+      <c r="B96" s="23"/>
     </row>
     <row r="97" spans="2:2">
-      <c r="B97" s="25"/>
+      <c r="B97" s="23"/>
     </row>
     <row r="98" spans="2:2">
-      <c r="B98" s="25"/>
+      <c r="B98" s="23"/>
     </row>
     <row r="99" spans="2:2">
-      <c r="B99" s="25"/>
+      <c r="B99" s="23"/>
     </row>
     <row r="100" spans="2:2">
-      <c r="B100" s="25"/>
+      <c r="B100" s="23"/>
     </row>
     <row r="101" spans="2:2">
-      <c r="B101" s="25"/>
+      <c r="B101" s="23"/>
     </row>
     <row r="102" spans="2:2">
-      <c r="B102" s="25"/>
+      <c r="B102" s="23"/>
     </row>
     <row r="103" spans="2:2">
-      <c r="B103" s="25"/>
+      <c r="B103" s="23"/>
     </row>
     <row r="104" spans="2:2">
-      <c r="B104" s="25"/>
+      <c r="B104" s="23"/>
     </row>
     <row r="105" spans="2:2">
-      <c r="B105" s="25"/>
+      <c r="B105" s="23"/>
     </row>
     <row r="106" spans="2:2">
-      <c r="B106" s="25"/>
+      <c r="B106" s="23"/>
     </row>
     <row r="107" spans="2:2">
-      <c r="B107" s="25"/>
+      <c r="B107" s="23"/>
     </row>
     <row r="108" spans="2:2">
-      <c r="B108" s="25"/>
+      <c r="B108" s="23"/>
     </row>
     <row r="109" spans="2:2">
-      <c r="B109" s="25"/>
+      <c r="B109" s="23"/>
     </row>
     <row r="110" spans="2:2">
-      <c r="B110" s="25"/>
+      <c r="B110" s="23"/>
     </row>
     <row r="111" spans="2:2">
-      <c r="B111" s="25"/>
+      <c r="B111" s="23"/>
     </row>
     <row r="112" spans="2:2">
-      <c r="B112" s="25"/>
+      <c r="B112" s="23"/>
     </row>
     <row r="113" spans="2:2">
-      <c r="B113" s="25"/>
+      <c r="B113" s="23"/>
     </row>
     <row r="114" spans="2:2">
-      <c r="B114" s="25"/>
+      <c r="B114" s="23"/>
     </row>
     <row r="115" spans="2:2">
-      <c r="B115" s="25"/>
+      <c r="B115" s="23"/>
     </row>
     <row r="116" spans="2:2">
-      <c r="B116" s="25"/>
+      <c r="B116" s="23"/>
     </row>
     <row r="117" spans="2:2">
-      <c r="B117" s="25"/>
+      <c r="B117" s="23"/>
     </row>
     <row r="118" spans="2:2">
-      <c r="B118" s="25"/>
+      <c r="B118" s="23"/>
     </row>
     <row r="119" spans="2:2">
-      <c r="B119" s="25"/>
+      <c r="B119" s="23"/>
     </row>
     <row r="120" spans="2:2">
-      <c r="B120" s="25"/>
+      <c r="B120" s="23"/>
     </row>
     <row r="121" spans="2:2">
-      <c r="B121" s="25"/>
+      <c r="B121" s="23"/>
     </row>
     <row r="122" spans="2:2">
-      <c r="B122" s="25"/>
+      <c r="B122" s="23"/>
     </row>
     <row r="123" spans="2:2">
-      <c r="B123" s="25"/>
+      <c r="B123" s="23"/>
     </row>
     <row r="124" spans="2:2">
-      <c r="B124" s="25"/>
+      <c r="B124" s="23"/>
     </row>
     <row r="125" spans="2:2">
-      <c r="B125" s="25"/>
+      <c r="B125" s="23"/>
     </row>
     <row r="126" spans="2:2">
-      <c r="B126" s="25"/>
+      <c r="B126" s="23"/>
     </row>
     <row r="127" spans="2:2">
-      <c r="B127" s="25"/>
+      <c r="B127" s="23"/>
     </row>
     <row r="128" spans="2:2">
-      <c r="B128" s="25"/>
+      <c r="B128" s="23"/>
     </row>
     <row r="129" spans="2:2">
-      <c r="B129" s="25"/>
+      <c r="B129" s="23"/>
     </row>
     <row r="130" spans="2:2">
-      <c r="B130" s="25"/>
+      <c r="B130" s="23"/>
     </row>
     <row r="131" spans="2:2">
-      <c r="B131" s="25"/>
+      <c r="B131" s="23"/>
     </row>
     <row r="132" spans="2:2">
-      <c r="B132" s="25"/>
+      <c r="B132" s="23"/>
     </row>
     <row r="133" spans="2:2">
-      <c r="B133" s="25"/>
+      <c r="B133" s="23"/>
     </row>
     <row r="134" spans="2:2">
-      <c r="B134" s="25"/>
+      <c r="B134" s="23"/>
     </row>
     <row r="135" spans="2:2">
-      <c r="B135" s="25"/>
+      <c r="B135" s="23"/>
     </row>
     <row r="136" spans="2:2">
-      <c r="B136" s="25"/>
+      <c r="B136" s="23"/>
     </row>
     <row r="137" spans="2:2">
-      <c r="B137" s="25"/>
+      <c r="B137" s="23"/>
     </row>
     <row r="138" spans="2:2">
-      <c r="B138" s="25"/>
+      <c r="B138" s="23"/>
     </row>
     <row r="139" spans="2:2">
-      <c r="B139" s="25"/>
+      <c r="B139" s="23"/>
     </row>
     <row r="140" spans="2:2">
-      <c r="B140" s="25"/>
+      <c r="B140" s="23"/>
     </row>
     <row r="141" spans="2:2">
-      <c r="B141" s="25"/>
+      <c r="B141" s="23"/>
     </row>
     <row r="142" spans="2:2">
-      <c r="B142" s="25"/>
+      <c r="B142" s="23"/>
     </row>
     <row r="143" spans="2:2">
-      <c r="B143" s="25"/>
+      <c r="B143" s="23"/>
     </row>
     <row r="144" spans="2:2">
-      <c r="B144" s="25"/>
+      <c r="B144" s="23"/>
     </row>
     <row r="145" spans="2:2">
-      <c r="B145" s="25"/>
+      <c r="B145" s="23"/>
     </row>
     <row r="146" spans="2:2">
-      <c r="B146" s="25"/>
+      <c r="B146" s="23"/>
     </row>
     <row r="147" spans="2:2">
-      <c r="B147" s="25"/>
+      <c r="B147" s="23"/>
     </row>
     <row r="148" spans="2:2">
-      <c r="B148" s="25"/>
+      <c r="B148" s="23"/>
     </row>
     <row r="149" spans="2:2">
-      <c r="B149" s="25"/>
+      <c r="B149" s="23"/>
     </row>
     <row r="150" spans="2:2">
-      <c r="B150" s="25"/>
+      <c r="B150" s="23"/>
     </row>
     <row r="151" spans="2:2">
-      <c r="B151" s="25"/>
+      <c r="B151" s="23"/>
     </row>
     <row r="152" spans="2:2">
-      <c r="B152" s="25"/>
+      <c r="B152" s="23"/>
     </row>
     <row r="153" spans="2:2">
-      <c r="B153" s="25"/>
+      <c r="B153" s="23"/>
     </row>
     <row r="154" spans="2:2">
-      <c r="B154" s="25"/>
+      <c r="B154" s="23"/>
     </row>
     <row r="155" spans="2:2">
-      <c r="B155" s="25"/>
+      <c r="B155" s="23"/>
     </row>
     <row r="156" spans="2:2">
-      <c r="B156" s="25"/>
+      <c r="B156" s="23"/>
     </row>
     <row r="157" spans="2:2">
-      <c r="B157" s="25"/>
+      <c r="B157" s="23"/>
     </row>
     <row r="158" spans="2:2">
-      <c r="B158" s="25"/>
+      <c r="B158" s="23"/>
     </row>
     <row r="159" spans="2:2">
-      <c r="B159" s="25"/>
+      <c r="B159" s="23"/>
     </row>
     <row r="160" spans="2:2">
-      <c r="B160" s="25"/>
+      <c r="B160" s="23"/>
     </row>
     <row r="161" spans="2:2">
-      <c r="B161" s="25"/>
+      <c r="B161" s="23"/>
     </row>
     <row r="162" spans="2:2">
-      <c r="B162" s="25"/>
+      <c r="B162" s="23"/>
     </row>
     <row r="163" spans="2:2">
-      <c r="B163" s="25"/>
+      <c r="B163" s="23"/>
     </row>
     <row r="164" spans="2:2">
-      <c r="B164" s="25"/>
+      <c r="B164" s="23"/>
     </row>
     <row r="165" spans="2:2">
-      <c r="B165" s="25"/>
+      <c r="B165" s="23"/>
     </row>
     <row r="166" spans="2:2">
-      <c r="B166" s="25"/>
+      <c r="B166" s="23"/>
     </row>
     <row r="167" spans="2:2">
-      <c r="B167" s="25"/>
+      <c r="B167" s="23"/>
     </row>
     <row r="168" spans="2:2">
-      <c r="B168" s="25"/>
+      <c r="B168" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="23">
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="C7:C21"/>
     <mergeCell ref="C22:C34"/>
     <mergeCell ref="C35:C38"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="C43:C46"/>
-    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C39:C46"/>
+    <mergeCell ref="C47:C54"/>
+    <mergeCell ref="C56:C57"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="D7:D10"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="D13:D15"/>
     <mergeCell ref="D16:D20"/>
+    <mergeCell ref="D22:D23"/>
     <mergeCell ref="D24:D25"/>
     <mergeCell ref="D26:D27"/>
     <mergeCell ref="D28:D30"/>
     <mergeCell ref="D31:D32"/>
     <mergeCell ref="D33:D34"/>
     <mergeCell ref="D35:D36"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="D39:D42"/>
     <mergeCell ref="D43:D46"/>
-    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D47:D54"/>
+    <mergeCell ref="D56:D57"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="0.98" bottom="0.98" header="0.51" footer="0.51"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="600" verticalDpi="600"/>
-  <headerFooter alignWithMargins="0"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -4074,1230 +4140,1230 @@
   <dimension ref="B1:L179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="1.63636363636364" style="3" customWidth="1"/>
-    <col min="2" max="2" width="4.45454545454545" style="4"/>
-    <col min="3" max="5" width="16.6363636363636" style="4" customWidth="1"/>
-    <col min="6" max="6" width="57.1818181818182" style="4" customWidth="1"/>
-    <col min="7" max="7" width="9" style="3"/>
-    <col min="8" max="8" width="10.4545454545455" style="5"/>
-    <col min="9" max="9" width="6.36363636363636" style="5"/>
-    <col min="10" max="10" width="22.0909090909091" style="6"/>
-    <col min="11" max="11" width="11.6363636363636" style="6"/>
-    <col min="12" max="12" width="33.4545454545455" style="6"/>
-    <col min="13" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="1.63636363636364" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.45454545454545" style="2" customWidth="1"/>
+    <col min="3" max="5" width="16.6363636363636" style="2" customWidth="1"/>
+    <col min="6" max="6" width="57.1818181818182" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.4545454545455" style="3" customWidth="1"/>
+    <col min="9" max="9" width="6.36363636363636" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.0909090909091" style="4" customWidth="1"/>
+    <col min="11" max="11" width="11.6363636363636" style="4" customWidth="1"/>
+    <col min="12" max="12" width="33.4545454545455" style="4" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="41.25" customHeight="1" spans="2:12">
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
     </row>
     <row r="2" ht="21" customHeight="1" spans="2:12">
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="34" customHeight="1" spans="2:12">
-      <c r="B4" s="14">
+      <c r="K3" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="34" customHeight="1" spans="2:12">
+      <c r="B4" s="12">
         <v>1</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="17">
+      <c r="D4" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="15">
         <v>43339</v>
       </c>
-      <c r="I4" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L4" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B5" s="20">
+      <c r="I4" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B5" s="18">
         <v>2</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="17">
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="15">
         <v>43339</v>
       </c>
-      <c r="I5" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L5" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="39" customHeight="1" spans="2:12">
-      <c r="B6" s="14">
+      <c r="I5" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="39" customHeight="1" spans="2:12">
+      <c r="B6" s="12">
         <v>3</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>163</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17">
+      <c r="C6" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="15">
         <v>43340</v>
       </c>
-      <c r="I6" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L6" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B7" s="20">
+      <c r="I6" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B7" s="18">
         <v>4</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="17">
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="G7" s="14"/>
+      <c r="H7" s="15">
         <v>43340</v>
       </c>
-      <c r="I7" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B8" s="14">
+      <c r="I7" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B8" s="12">
         <v>5</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="17">
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="F8" s="19"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="15">
         <v>43339</v>
       </c>
-      <c r="I8" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L8" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B9" s="20">
+      <c r="I8" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B9" s="18">
         <v>6</v>
       </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="E9" s="21" t="s">
+      <c r="C9" s="19"/>
+      <c r="D9" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="15">
+        <v>43339</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B10" s="12">
+        <v>7</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="15">
+        <v>43340</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L10" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B11" s="18">
+        <v>8</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="15">
+        <v>43340</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L11" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B12" s="12">
+        <v>9</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="15">
+        <v>43341</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L12" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B13" s="18">
+        <v>10</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="15">
+        <v>43339</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B14" s="12">
+        <v>11</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="G14" s="14"/>
+      <c r="H14" s="15">
+        <v>43339</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L14" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B15" s="18">
+        <v>12</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15" s="19"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="15">
+        <v>43340</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L15" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B16" s="12">
+        <v>13</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="15">
+        <v>43340</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L16" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B17" s="18">
+        <v>14</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="F17" s="19"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="15">
+        <v>43339</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B18" s="12">
+        <v>15</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D18" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="F9" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="17">
-        <v>43339</v>
-      </c>
-      <c r="I9" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L9" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B10" s="14">
-        <v>7</v>
-      </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="F10" s="21" t="s">
+      <c r="E18" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="G18" s="14"/>
+      <c r="H18" s="15">
+        <v>43340</v>
+      </c>
+      <c r="I18" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="17">
+      <c r="J18" s="17"/>
+      <c r="K18" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L18" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B19" s="18">
+        <v>16</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="G19" s="14"/>
+      <c r="H19" s="15">
         <v>43340</v>
       </c>
-      <c r="I10" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L10" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B11" s="20">
-        <v>8</v>
-      </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21" t="s">
+      <c r="I19" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="F11" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="17">
-        <v>43340</v>
-      </c>
-      <c r="I11" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L11" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B12" s="14">
-        <v>9</v>
-      </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="17">
-        <v>43341</v>
-      </c>
-      <c r="I12" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L12" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B13" s="20">
-        <v>10</v>
-      </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="17">
-        <v>43339</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L13" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B14" s="14">
-        <v>11</v>
-      </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="17">
-        <v>43339</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L14" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B15" s="20">
-        <v>12</v>
-      </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="17">
-        <v>43340</v>
-      </c>
-      <c r="I15" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L15" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B16" s="14">
-        <v>13</v>
-      </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="17">
-        <v>43340</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L16" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B17" s="20">
-        <v>14</v>
-      </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21" t="s">
-        <v>184</v>
-      </c>
-      <c r="F17" s="21"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="17">
-        <v>43339</v>
-      </c>
-      <c r="I17" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L17" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B18" s="14">
-        <v>15</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="G18" s="16"/>
-      <c r="H18" s="17">
-        <v>43340</v>
-      </c>
-      <c r="I18" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L18" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B19" s="20">
-        <v>16</v>
-      </c>
-      <c r="C19" s="21"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="17">
-        <v>43340</v>
-      </c>
-      <c r="I19" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L19" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B20" s="14">
+      <c r="L19" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B20" s="12">
         <v>17</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="17">
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="F20" s="19"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="15">
         <v>43342</v>
       </c>
-      <c r="I20" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L20" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B21" s="20">
+      <c r="I20" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B21" s="18">
         <v>18</v>
       </c>
-      <c r="C21" s="21" t="s">
-        <v>189</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="17">
+      <c r="C21" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="G21" s="14"/>
+      <c r="H21" s="15">
         <v>43342</v>
       </c>
-      <c r="I21" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L21" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B22" s="14">
+      <c r="I21" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J21" s="17"/>
+      <c r="K21" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B22" s="12">
         <v>19</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="F22" s="21"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="17">
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="F22" s="19"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="15">
         <v>43342</v>
       </c>
-      <c r="I22" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L22" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B23" s="20">
+      <c r="I22" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J22" s="17"/>
+      <c r="K22" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B23" s="18">
         <v>20</v>
       </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="F23" s="21"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="17">
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="F23" s="19"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="15">
         <v>43342</v>
       </c>
-      <c r="I23" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L23" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B24" s="14">
+      <c r="I23" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B24" s="12">
         <v>21</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="F24" s="21"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="17">
+      <c r="C24" s="19"/>
+      <c r="D24" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="F24" s="19"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="15">
         <v>43345</v>
       </c>
-      <c r="I24" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="L24" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B25" s="14"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="17">
+      <c r="I24" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L24" s="17" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B25" s="12"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="15">
         <v>43347</v>
       </c>
-      <c r="I25" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="J25" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="K25" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="L25" s="19" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B26" s="20"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="G26" s="16"/>
-      <c r="H26" s="17">
+      <c r="I25" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="L25" s="17" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="G26" s="14"/>
+      <c r="H26" s="15">
         <v>43345</v>
       </c>
-      <c r="I26" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="L26" s="19" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B27" s="20"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="G27" s="16"/>
-      <c r="H27" s="17">
+      <c r="I26" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="20.15" customHeight="1" spans="2:12">
+      <c r="B27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="G27" s="14"/>
+      <c r="H27" s="15">
         <v>43347</v>
       </c>
-      <c r="I27" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="L27" s="19" t="s">
-        <v>198</v>
+      <c r="I27" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="L27" s="17" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="28" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B28" s="22"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="17">
+      <c r="B28" s="20"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="15">
         <v>43346</v>
       </c>
-      <c r="I28" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="J28" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="K28" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="L28" s="19" t="s">
-        <v>204</v>
+      <c r="I28" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="L28" s="17" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="29" ht="20.15" customHeight="1" spans="2:12">
-      <c r="B29" s="25"/>
-      <c r="H29" s="17">
+      <c r="B29" s="23"/>
+      <c r="H29" s="15">
         <v>43346</v>
       </c>
-      <c r="I29" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="L29" s="19" t="s">
-        <v>205</v>
+      <c r="I29" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="L29" s="17" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="2:12">
-      <c r="B30" s="25"/>
-      <c r="H30" s="17">
+      <c r="B30" s="23"/>
+      <c r="H30" s="15">
         <v>43357</v>
       </c>
-      <c r="I30" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="J30" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="K30" s="19"/>
-      <c r="L30" s="19" t="s">
-        <v>208</v>
+      <c r="I30" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="J30" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="K30" s="17"/>
+      <c r="L30" s="17" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="2:12">
-      <c r="B31" s="25"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="K31" s="19"/>
-      <c r="L31" s="19" t="s">
-        <v>198</v>
+      <c r="B31" s="23"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="K31" s="17"/>
+      <c r="L31" s="17" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="32" spans="2:12">
-      <c r="B32" s="25"/>
+      <c r="B32" s="23"/>
     </row>
     <row r="33" spans="2:2">
-      <c r="B33" s="25"/>
+      <c r="B33" s="23"/>
     </row>
     <row r="34" spans="2:2">
-      <c r="B34" s="25"/>
+      <c r="B34" s="23"/>
     </row>
     <row r="35" spans="2:2">
-      <c r="B35" s="25"/>
+      <c r="B35" s="23"/>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" s="25"/>
+      <c r="B36" s="23"/>
     </row>
     <row r="37" spans="2:2">
-      <c r="B37" s="25"/>
+      <c r="B37" s="23"/>
     </row>
     <row r="38" spans="2:2">
-      <c r="B38" s="25"/>
+      <c r="B38" s="23"/>
     </row>
     <row r="39" spans="2:2">
-      <c r="B39" s="25"/>
+      <c r="B39" s="23"/>
     </row>
     <row r="40" spans="2:2">
-      <c r="B40" s="25"/>
+      <c r="B40" s="23"/>
     </row>
     <row r="41" spans="2:2">
-      <c r="B41" s="25"/>
+      <c r="B41" s="23"/>
     </row>
     <row r="42" spans="2:2">
-      <c r="B42" s="25"/>
+      <c r="B42" s="23"/>
     </row>
     <row r="43" spans="2:2">
-      <c r="B43" s="25"/>
+      <c r="B43" s="23"/>
     </row>
     <row r="44" spans="2:2">
-      <c r="B44" s="25"/>
+      <c r="B44" s="23"/>
     </row>
     <row r="45" spans="2:2">
-      <c r="B45" s="25"/>
+      <c r="B45" s="23"/>
     </row>
     <row r="46" spans="2:2">
-      <c r="B46" s="25"/>
+      <c r="B46" s="23"/>
     </row>
     <row r="47" spans="2:2">
-      <c r="B47" s="25"/>
+      <c r="B47" s="23"/>
     </row>
     <row r="48" spans="2:2">
-      <c r="B48" s="25"/>
+      <c r="B48" s="23"/>
     </row>
     <row r="49" spans="2:2">
-      <c r="B49" s="25"/>
+      <c r="B49" s="23"/>
     </row>
     <row r="50" spans="2:2">
-      <c r="B50" s="25"/>
+      <c r="B50" s="23"/>
     </row>
     <row r="51" spans="2:2">
-      <c r="B51" s="25"/>
+      <c r="B51" s="23"/>
     </row>
     <row r="52" spans="2:2">
-      <c r="B52" s="25"/>
+      <c r="B52" s="23"/>
     </row>
     <row r="53" spans="2:2">
-      <c r="B53" s="25"/>
+      <c r="B53" s="23"/>
     </row>
     <row r="54" spans="2:2">
-      <c r="B54" s="25"/>
+      <c r="B54" s="23"/>
     </row>
     <row r="55" spans="2:2">
-      <c r="B55" s="25"/>
+      <c r="B55" s="23"/>
     </row>
     <row r="56" spans="2:2">
-      <c r="B56" s="25"/>
+      <c r="B56" s="23"/>
     </row>
     <row r="57" spans="2:2">
-      <c r="B57" s="25"/>
+      <c r="B57" s="23"/>
     </row>
     <row r="58" spans="2:2">
-      <c r="B58" s="25"/>
+      <c r="B58" s="23"/>
     </row>
     <row r="59" spans="2:2">
-      <c r="B59" s="25"/>
+      <c r="B59" s="23"/>
     </row>
     <row r="60" spans="2:2">
-      <c r="B60" s="25"/>
+      <c r="B60" s="23"/>
     </row>
     <row r="61" spans="2:2">
-      <c r="B61" s="25"/>
+      <c r="B61" s="23"/>
     </row>
     <row r="62" spans="2:2">
-      <c r="B62" s="25"/>
+      <c r="B62" s="23"/>
     </row>
     <row r="63" spans="2:2">
-      <c r="B63" s="25"/>
+      <c r="B63" s="23"/>
     </row>
     <row r="64" spans="2:2">
-      <c r="B64" s="25"/>
+      <c r="B64" s="23"/>
     </row>
     <row r="65" spans="2:2">
-      <c r="B65" s="25"/>
+      <c r="B65" s="23"/>
     </row>
     <row r="66" spans="2:2">
-      <c r="B66" s="25"/>
+      <c r="B66" s="23"/>
     </row>
     <row r="67" spans="2:2">
-      <c r="B67" s="25"/>
+      <c r="B67" s="23"/>
     </row>
     <row r="68" spans="2:2">
-      <c r="B68" s="25"/>
+      <c r="B68" s="23"/>
     </row>
     <row r="69" spans="2:2">
-      <c r="B69" s="25"/>
+      <c r="B69" s="23"/>
     </row>
     <row r="70" spans="2:2">
-      <c r="B70" s="25"/>
+      <c r="B70" s="23"/>
     </row>
     <row r="71" spans="2:2">
-      <c r="B71" s="25"/>
+      <c r="B71" s="23"/>
     </row>
     <row r="72" spans="2:2">
-      <c r="B72" s="25"/>
+      <c r="B72" s="23"/>
     </row>
     <row r="73" spans="2:2">
-      <c r="B73" s="25"/>
+      <c r="B73" s="23"/>
     </row>
     <row r="74" spans="2:2">
-      <c r="B74" s="25"/>
+      <c r="B74" s="23"/>
     </row>
     <row r="75" spans="2:2">
-      <c r="B75" s="25"/>
+      <c r="B75" s="23"/>
     </row>
     <row r="76" spans="2:2">
-      <c r="B76" s="25"/>
+      <c r="B76" s="23"/>
     </row>
     <row r="77" spans="2:2">
-      <c r="B77" s="25"/>
+      <c r="B77" s="23"/>
     </row>
     <row r="78" spans="2:2">
-      <c r="B78" s="25"/>
+      <c r="B78" s="23"/>
     </row>
     <row r="79" spans="2:2">
-      <c r="B79" s="25"/>
+      <c r="B79" s="23"/>
     </row>
     <row r="80" spans="2:2">
-      <c r="B80" s="25"/>
+      <c r="B80" s="23"/>
     </row>
     <row r="81" spans="2:2">
-      <c r="B81" s="25"/>
+      <c r="B81" s="23"/>
     </row>
     <row r="82" spans="2:2">
-      <c r="B82" s="25"/>
+      <c r="B82" s="23"/>
     </row>
     <row r="83" spans="2:2">
-      <c r="B83" s="25"/>
+      <c r="B83" s="23"/>
     </row>
     <row r="84" spans="2:2">
-      <c r="B84" s="25"/>
+      <c r="B84" s="23"/>
     </row>
     <row r="85" spans="2:2">
-      <c r="B85" s="25"/>
+      <c r="B85" s="23"/>
     </row>
     <row r="86" spans="2:2">
-      <c r="B86" s="25"/>
+      <c r="B86" s="23"/>
     </row>
     <row r="87" spans="2:2">
-      <c r="B87" s="25"/>
+      <c r="B87" s="23"/>
     </row>
     <row r="88" spans="2:2">
-      <c r="B88" s="25"/>
+      <c r="B88" s="23"/>
     </row>
     <row r="89" spans="2:2">
-      <c r="B89" s="25"/>
+      <c r="B89" s="23"/>
     </row>
     <row r="90" spans="2:2">
-      <c r="B90" s="25"/>
+      <c r="B90" s="23"/>
     </row>
     <row r="91" spans="2:2">
-      <c r="B91" s="25"/>
+      <c r="B91" s="23"/>
     </row>
     <row r="92" spans="2:2">
-      <c r="B92" s="25"/>
+      <c r="B92" s="23"/>
     </row>
     <row r="93" spans="2:2">
-      <c r="B93" s="25"/>
+      <c r="B93" s="23"/>
     </row>
     <row r="94" spans="2:2">
-      <c r="B94" s="25"/>
+      <c r="B94" s="23"/>
     </row>
     <row r="95" spans="2:2">
-      <c r="B95" s="25"/>
+      <c r="B95" s="23"/>
     </row>
     <row r="96" spans="2:2">
-      <c r="B96" s="25"/>
+      <c r="B96" s="23"/>
     </row>
     <row r="97" spans="2:2">
-      <c r="B97" s="25"/>
+      <c r="B97" s="23"/>
     </row>
     <row r="98" spans="2:2">
-      <c r="B98" s="25"/>
+      <c r="B98" s="23"/>
     </row>
     <row r="99" spans="2:2">
-      <c r="B99" s="25"/>
+      <c r="B99" s="23"/>
     </row>
     <row r="100" spans="2:2">
-      <c r="B100" s="25"/>
+      <c r="B100" s="23"/>
     </row>
     <row r="101" spans="2:2">
-      <c r="B101" s="25"/>
+      <c r="B101" s="23"/>
     </row>
     <row r="102" spans="2:2">
-      <c r="B102" s="25"/>
+      <c r="B102" s="23"/>
     </row>
     <row r="103" spans="2:2">
-      <c r="B103" s="25"/>
+      <c r="B103" s="23"/>
     </row>
     <row r="104" spans="2:2">
-      <c r="B104" s="25"/>
+      <c r="B104" s="23"/>
     </row>
     <row r="105" spans="2:2">
-      <c r="B105" s="25"/>
+      <c r="B105" s="23"/>
     </row>
     <row r="106" spans="2:2">
-      <c r="B106" s="25"/>
+      <c r="B106" s="23"/>
     </row>
     <row r="107" spans="2:2">
-      <c r="B107" s="25"/>
+      <c r="B107" s="23"/>
     </row>
     <row r="108" spans="2:2">
-      <c r="B108" s="25"/>
+      <c r="B108" s="23"/>
     </row>
     <row r="109" spans="2:2">
-      <c r="B109" s="25"/>
+      <c r="B109" s="23"/>
     </row>
     <row r="110" spans="2:2">
-      <c r="B110" s="25"/>
+      <c r="B110" s="23"/>
     </row>
     <row r="111" spans="2:2">
-      <c r="B111" s="25"/>
+      <c r="B111" s="23"/>
     </row>
     <row r="112" spans="2:2">
-      <c r="B112" s="25"/>
+      <c r="B112" s="23"/>
     </row>
     <row r="113" spans="2:2">
-      <c r="B113" s="25"/>
+      <c r="B113" s="23"/>
     </row>
     <row r="114" spans="2:2">
-      <c r="B114" s="25"/>
+      <c r="B114" s="23"/>
     </row>
     <row r="115" spans="2:2">
-      <c r="B115" s="25"/>
+      <c r="B115" s="23"/>
     </row>
     <row r="116" spans="2:2">
-      <c r="B116" s="25"/>
+      <c r="B116" s="23"/>
     </row>
     <row r="117" spans="2:2">
-      <c r="B117" s="25"/>
+      <c r="B117" s="23"/>
     </row>
     <row r="118" spans="2:2">
-      <c r="B118" s="25"/>
+      <c r="B118" s="23"/>
     </row>
     <row r="119" spans="2:2">
-      <c r="B119" s="25"/>
+      <c r="B119" s="23"/>
     </row>
     <row r="120" spans="2:2">
-      <c r="B120" s="25"/>
+      <c r="B120" s="23"/>
     </row>
     <row r="121" spans="2:2">
-      <c r="B121" s="25"/>
+      <c r="B121" s="23"/>
     </row>
     <row r="122" spans="2:2">
-      <c r="B122" s="25"/>
+      <c r="B122" s="23"/>
     </row>
     <row r="123" spans="2:2">
-      <c r="B123" s="25"/>
+      <c r="B123" s="23"/>
     </row>
     <row r="124" spans="2:2">
-      <c r="B124" s="25"/>
+      <c r="B124" s="23"/>
     </row>
     <row r="125" spans="2:2">
-      <c r="B125" s="25"/>
+      <c r="B125" s="23"/>
     </row>
     <row r="126" spans="2:2">
-      <c r="B126" s="25"/>
+      <c r="B126" s="23"/>
     </row>
     <row r="127" spans="2:2">
-      <c r="B127" s="25"/>
+      <c r="B127" s="23"/>
     </row>
     <row r="128" spans="2:2">
-      <c r="B128" s="25"/>
+      <c r="B128" s="23"/>
     </row>
     <row r="129" spans="2:2">
-      <c r="B129" s="25"/>
+      <c r="B129" s="23"/>
     </row>
     <row r="130" spans="2:2">
-      <c r="B130" s="25"/>
+      <c r="B130" s="23"/>
     </row>
     <row r="131" spans="2:2">
-      <c r="B131" s="25"/>
+      <c r="B131" s="23"/>
     </row>
     <row r="132" spans="2:2">
-      <c r="B132" s="25"/>
+      <c r="B132" s="23"/>
     </row>
     <row r="133" spans="2:2">
-      <c r="B133" s="25"/>
+      <c r="B133" s="23"/>
     </row>
     <row r="134" spans="2:2">
-      <c r="B134" s="25"/>
+      <c r="B134" s="23"/>
     </row>
     <row r="135" spans="2:2">
-      <c r="B135" s="25"/>
+      <c r="B135" s="23"/>
     </row>
     <row r="136" spans="2:2">
-      <c r="B136" s="25"/>
+      <c r="B136" s="23"/>
     </row>
     <row r="137" spans="2:2">
-      <c r="B137" s="25"/>
+      <c r="B137" s="23"/>
     </row>
     <row r="138" spans="2:2">
-      <c r="B138" s="25"/>
+      <c r="B138" s="23"/>
     </row>
     <row r="139" spans="2:2">
-      <c r="B139" s="25"/>
+      <c r="B139" s="23"/>
     </row>
     <row r="140" spans="2:2">
-      <c r="B140" s="25"/>
+      <c r="B140" s="23"/>
     </row>
     <row r="141" spans="2:2">
-      <c r="B141" s="25"/>
+      <c r="B141" s="23"/>
     </row>
     <row r="142" spans="2:2">
-      <c r="B142" s="25"/>
+      <c r="B142" s="23"/>
     </row>
     <row r="143" spans="2:2">
-      <c r="B143" s="25"/>
+      <c r="B143" s="23"/>
     </row>
     <row r="144" spans="2:2">
-      <c r="B144" s="25"/>
+      <c r="B144" s="23"/>
     </row>
     <row r="145" spans="2:2">
-      <c r="B145" s="25"/>
+      <c r="B145" s="23"/>
     </row>
     <row r="146" spans="2:2">
-      <c r="B146" s="25"/>
+      <c r="B146" s="23"/>
     </row>
     <row r="147" spans="2:2">
-      <c r="B147" s="25"/>
+      <c r="B147" s="23"/>
     </row>
     <row r="148" spans="2:2">
-      <c r="B148" s="25"/>
+      <c r="B148" s="23"/>
     </row>
     <row r="149" spans="2:2">
-      <c r="B149" s="25"/>
+      <c r="B149" s="23"/>
     </row>
     <row r="150" spans="2:2">
-      <c r="B150" s="25"/>
+      <c r="B150" s="23"/>
     </row>
     <row r="151" spans="2:2">
-      <c r="B151" s="25"/>
+      <c r="B151" s="23"/>
     </row>
     <row r="152" spans="2:2">
-      <c r="B152" s="25"/>
+      <c r="B152" s="23"/>
     </row>
     <row r="153" spans="2:2">
-      <c r="B153" s="25"/>
+      <c r="B153" s="23"/>
     </row>
     <row r="154" spans="2:2">
-      <c r="B154" s="25"/>
+      <c r="B154" s="23"/>
     </row>
     <row r="155" spans="2:2">
-      <c r="B155" s="25"/>
+      <c r="B155" s="23"/>
     </row>
     <row r="156" spans="2:2">
-      <c r="B156" s="25"/>
+      <c r="B156" s="23"/>
     </row>
     <row r="157" spans="2:2">
-      <c r="B157" s="25"/>
+      <c r="B157" s="23"/>
     </row>
     <row r="158" spans="2:2">
-      <c r="B158" s="25"/>
+      <c r="B158" s="23"/>
     </row>
     <row r="159" spans="2:2">
-      <c r="B159" s="25"/>
+      <c r="B159" s="23"/>
     </row>
     <row r="160" spans="2:2">
-      <c r="B160" s="25"/>
+      <c r="B160" s="23"/>
     </row>
     <row r="161" spans="2:2">
-      <c r="B161" s="25"/>
+      <c r="B161" s="23"/>
     </row>
     <row r="162" spans="2:2">
-      <c r="B162" s="25"/>
+      <c r="B162" s="23"/>
     </row>
     <row r="163" spans="2:2">
-      <c r="B163" s="25"/>
+      <c r="B163" s="23"/>
     </row>
     <row r="164" spans="2:2">
-      <c r="B164" s="25"/>
+      <c r="B164" s="23"/>
     </row>
     <row r="165" spans="2:2">
-      <c r="B165" s="25"/>
+      <c r="B165" s="23"/>
     </row>
     <row r="166" spans="2:2">
-      <c r="B166" s="25"/>
+      <c r="B166" s="23"/>
     </row>
     <row r="167" spans="2:2">
-      <c r="B167" s="25"/>
+      <c r="B167" s="23"/>
     </row>
     <row r="168" spans="2:2">
-      <c r="B168" s="25"/>
+      <c r="B168" s="23"/>
     </row>
     <row r="169" spans="2:2">
-      <c r="B169" s="25"/>
+      <c r="B169" s="23"/>
     </row>
     <row r="170" spans="2:2">
-      <c r="B170" s="25"/>
+      <c r="B170" s="23"/>
     </row>
     <row r="171" spans="2:2">
-      <c r="B171" s="25"/>
+      <c r="B171" s="23"/>
     </row>
     <row r="172" spans="2:2">
-      <c r="B172" s="25"/>
+      <c r="B172" s="23"/>
     </row>
     <row r="173" spans="2:2">
-      <c r="B173" s="25"/>
+      <c r="B173" s="23"/>
     </row>
     <row r="174" spans="2:2">
-      <c r="B174" s="25"/>
+      <c r="B174" s="23"/>
     </row>
     <row r="175" spans="2:2">
-      <c r="B175" s="25"/>
+      <c r="B175" s="23"/>
     </row>
     <row r="176" spans="2:2">
-      <c r="B176" s="25"/>
+      <c r="B176" s="23"/>
     </row>
     <row r="177" spans="2:2">
-      <c r="B177" s="25"/>
+      <c r="B177" s="23"/>
     </row>
     <row r="178" spans="2:2">
-      <c r="B178" s="25"/>
+      <c r="B178" s="23"/>
     </row>
     <row r="179" spans="2:2">
-      <c r="B179" s="25"/>
+      <c r="B179" s="23"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="0.98" bottom="0.98" header="0.51" footer="0.51"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="600" verticalDpi="600"/>
-  <headerFooter alignWithMargins="0"/>
+  <headerFooter/>
 </worksheet>
 </file>